--- a/LinkedIn_Structural.xlsx
+++ b/LinkedIn_Structural.xlsx
@@ -2313,12 +2313,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>عزالدين</t>
+          <t>Ezzeldin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>البكري</t>
+          <t>Albakri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
